--- a/nyahururu/Copy of aug disbursement loan balances.xlsx
+++ b/nyahururu/Copy of aug disbursement loan balances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\KashLeo data\nyahururu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9D00E66-70CE-4D57-89FE-66156C7BB7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66E56DE-12A1-4963-8C2E-984D462CA103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5140" yWindow="3150" windowWidth="14400" windowHeight="7270" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="1" r:id="rId1"/>
@@ -2820,7 +2820,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3545,7 +3545,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.54296875" style="15" customWidth="1"/>
     <col min="2" max="2" width="10.54296875" style="27" customWidth="1"/>
@@ -3565,7 +3565,7 @@
     <col min="17" max="16384" width="9.1796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="36">
+    <row r="1" spans="1:17" ht="36" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Q1" s="14"/>
     </row>
-    <row r="2" spans="1:17" hidden="1">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>13</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:65" s="24" customFormat="1" hidden="1">
+    <row r="17" spans="1:65" s="24" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -4523,7 +4523,7 @@
       <c r="BL17" s="23"/>
       <c r="BM17" s="23"/>
     </row>
-    <row r="18" spans="1:65" s="24" customFormat="1" hidden="1">
+    <row r="18" spans="1:65" s="24" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -4626,7 +4626,7 @@
       <c r="BL18" s="23"/>
       <c r="BM18" s="23"/>
     </row>
-    <row r="19" spans="1:65" hidden="1">
+    <row r="19" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -4729,7 +4729,7 @@
       <c r="BL19" s="23"/>
       <c r="BM19" s="23"/>
     </row>
-    <row r="20" spans="1:65" hidden="1">
+    <row r="20" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -4832,7 +4832,7 @@
       <c r="BL20" s="23"/>
       <c r="BM20" s="23"/>
     </row>
-    <row r="21" spans="1:65" hidden="1">
+    <row r="21" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:65" hidden="1">
+    <row r="22" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:65" hidden="1">
+    <row r="23" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:65" hidden="1">
+    <row r="24" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:65" hidden="1">
+    <row r="25" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:65" hidden="1">
+    <row r="26" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:65" hidden="1">
+    <row r="27" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:65" hidden="1">
+    <row r="28" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>27</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:65" hidden="1">
+    <row r="29" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:65" hidden="1">
+    <row r="30" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:65" hidden="1">
+    <row r="31" spans="1:65" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -5425,7 +5425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:65" s="53" customFormat="1">
+    <row r="32" spans="1:65" s="53" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="43">
         <v>31</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>4330</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>33</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>39</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" s="53" customFormat="1" hidden="1">
+    <row r="41" spans="1:16" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="43">
         <v>40</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="53" customFormat="1" hidden="1">
+    <row r="42" spans="1:16" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="43">
         <v>41</v>
       </c>
@@ -6019,21 +6019,21 @@
         <v>5181</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="16"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="16"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F48" s="25" t="s">
         <v>265</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>18335</v>
       </c>
     </row>
-    <row r="49" spans="6:16">
+    <row r="49" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F49" s="25"/>
       <c r="G49" s="25"/>
       <c r="H49" s="25"/>
@@ -6082,20 +6082,20 @@
       <c r="O49" s="25"/>
       <c r="P49" s="25"/>
     </row>
-    <row r="62" spans="6:16" ht="13.5" customHeight="1"/>
-    <row r="63" spans="6:16" ht="13.5" customHeight="1"/>
-    <row r="64" spans="6:16" ht="13.5" customHeight="1"/>
-    <row r="560" spans="8:8">
+    <row r="62" spans="6:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="6:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="6:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H560" s="15" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="561" spans="8:8">
+    <row r="561" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H561" s="15" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="1048576" spans="9:13">
+    <row r="1048576" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I1048576" s="28">
         <f>SUM(I2:I1048575)</f>
         <v>928000</v>
@@ -6122,7 +6122,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N157"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.81640625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -6140,7 +6140,7 @@
     <col min="14" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="36">
+    <row r="1" spans="1:14" ht="36" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="97">
         <v>46089</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="97">
         <v>46089</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="97">
         <v>46089</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="97">
         <v>46089</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="97">
         <v>46089</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="97">
         <v>46088</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="97">
         <v>46089</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="97">
         <v>46089</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="97">
         <v>46089</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="97">
         <v>46089</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="97">
         <v>46089</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="97">
         <v>46089</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="97">
         <v>46089</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="97">
         <v>46089</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="97">
         <v>46089</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="97">
         <v>46089</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="97">
         <v>46120</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="97">
         <v>46120</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="97">
         <v>46120</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="97">
         <v>46120</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="97">
         <v>46120</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="97">
         <v>46120</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="97">
         <v>46150</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="97">
         <v>46150</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="97">
         <v>46150</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="97">
         <v>46181</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="97">
         <v>46181</v>
       </c>
@@ -7372,7 +7372,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="97">
         <v>46211</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="97">
         <v>46211</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="97">
         <v>46211</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="97">
         <v>46211</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="97">
         <v>46211</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="97">
         <v>46211</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="97">
         <v>46211</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="97">
         <v>46211</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="97">
         <v>46211</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="97">
         <v>46211</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="97">
         <v>46303</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="97">
         <v>46303</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="97">
         <v>46303</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="97">
         <v>46303</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="97">
         <v>46303</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="97">
         <v>46303</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="97">
         <v>46303</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="97">
         <v>46303</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="97">
         <v>46303</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="97">
         <v>46303</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="97">
         <v>46303</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="97">
         <v>46303</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="97">
         <v>46303</v>
       </c>
@@ -8384,7 +8384,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="97">
         <v>46334</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="97">
         <v>46334</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="97">
         <v>46334</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="97">
         <v>46334</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="97">
         <v>46334</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="97">
         <v>46334</v>
       </c>
@@ -8648,7 +8648,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="97">
         <v>46334</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="97">
         <v>46334</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="97">
         <v>46334</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="97">
         <v>46364</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="97">
         <v>46364</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="97">
         <v>46364</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="97">
         <v>46364</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="97">
         <v>46364</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="97">
         <v>46364</v>
       </c>
@@ -9044,7 +9044,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="97">
         <v>46364</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="97">
         <v>46364</v>
       </c>
@@ -9132,7 +9132,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="97">
         <v>46364</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="97">
         <v>46364</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="97" t="s">
         <v>848</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>848</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="97" t="s">
         <v>848</v>
       </c>
@@ -9352,7 +9352,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="97" t="s">
         <v>848</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="97" t="s">
         <v>848</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="97" t="s">
         <v>848</v>
       </c>
@@ -9484,7 +9484,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="97" t="s">
         <v>848</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="97" t="s">
         <v>848</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="97" t="s">
         <v>855</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="97" t="s">
         <v>859</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>859</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>859</v>
       </c>
@@ -9748,7 +9748,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="97" t="s">
         <v>860</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>860</v>
       </c>
@@ -9836,7 +9836,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>860</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="97" t="s">
         <v>860</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>860</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="97" t="s">
         <v>860</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>860</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>863</v>
       </c>
@@ -10100,7 +10100,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>864</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>864</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="97" t="s">
         <v>864</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>864</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>864</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="97" t="s">
         <v>864</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>864</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>864</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>866</v>
       </c>
@@ -10496,7 +10496,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>866</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>866</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>866</v>
       </c>
@@ -10628,7 +10628,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>866</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>871</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="98" t="s">
         <v>871</v>
       </c>
@@ -10760,7 +10760,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>871</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>871</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>877</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>877</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>877</v>
       </c>
@@ -10980,7 +10980,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="97" t="s">
         <v>880</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>880</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>880</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>880</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>880</v>
       </c>
@@ -11200,7 +11200,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="97" t="s">
         <v>880</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>880</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>880</v>
       </c>
@@ -11332,7 +11332,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>880</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="97" t="s">
         <v>880</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>880</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>887</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>887</v>
       </c>
@@ -11552,7 +11552,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>887</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>887</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>887</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>887</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>887</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>887</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>898</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>898</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>898</v>
       </c>
@@ -11948,7 +11948,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="97" t="s">
         <v>898</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>898</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>899</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="97" t="s">
         <v>898</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>902</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>902</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>902</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>902</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>902</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>902</v>
       </c>
@@ -12388,7 +12388,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="97" t="s">
         <v>902</v>
       </c>
@@ -12432,7 +12432,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>907</v>
       </c>
@@ -12476,7 +12476,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>907</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>907</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="97" t="s">
         <v>907</v>
       </c>
@@ -12608,7 +12608,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>912</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>912</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="97" t="s">
         <v>912</v>
       </c>
@@ -12740,7 +12740,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>912</v>
       </c>
@@ -12784,7 +12784,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>912</v>
       </c>
@@ -12828,7 +12828,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="97" t="s">
         <v>912</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="97" t="s">
         <v>912</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>912</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>912</v>
       </c>
@@ -13004,7 +13004,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="F157">
         <f>SUM(F2:F156)</f>
         <v>1418000</v>
@@ -13043,7 +13043,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A2:P26"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
@@ -13057,7 +13057,7 @@
     <col min="10" max="10" width="5.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="100" t="s">
         <v>880</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="100" t="s">
         <v>880</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="100" t="s">
         <v>887</v>
       </c>
@@ -13207,7 +13207,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="100" t="s">
         <v>887</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="100" t="s">
         <v>887</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="100" t="s">
         <v>887</v>
       </c>
@@ -13351,7 +13351,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="100" t="s">
         <v>887</v>
       </c>
@@ -13397,7 +13397,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="100" t="s">
         <v>898</v>
       </c>
@@ -13445,7 +13445,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="100" t="s">
         <v>898</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="100" t="s">
         <v>899</v>
       </c>
@@ -13543,7 +13543,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="100" t="s">
         <v>902</v>
       </c>
@@ -13589,7 +13589,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="100" t="s">
         <v>902</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="100" t="s">
         <v>902</v>
       </c>
@@ -13687,7 +13687,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="100" t="s">
         <v>902</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="100" t="s">
         <v>902</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="100" t="s">
         <v>907</v>
       </c>
@@ -13835,7 +13835,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="100" t="s">
         <v>907</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="99" t="s">
         <v>907</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="100" t="s">
         <v>912</v>
       </c>
@@ -13981,7 +13981,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="99" t="s">
         <v>912</v>
       </c>
@@ -14029,7 +14029,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="100" t="s">
         <v>912</v>
       </c>
@@ -14077,7 +14077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="100" t="s">
         <v>912</v>
       </c>
@@ -14125,7 +14125,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="100" t="s">
         <v>912</v>
       </c>
@@ -14173,7 +14173,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="100"/>
       <c r="B25" s="100"/>
       <c r="C25" s="100"/>
@@ -14191,7 +14191,7 @@
       <c r="O25" s="100"/>
       <c r="P25" s="100"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="100"/>
       <c r="B26" s="100"/>
       <c r="C26" s="100"/>
@@ -14218,15 +14218,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.26953125" customWidth="1"/>
     <col min="3" max="3" width="17.08984375" customWidth="1"/>
     <col min="5" max="5" width="19.453125" customWidth="1"/>
     <col min="6" max="6" width="14.90625" customWidth="1"/>
+    <col min="14" max="14" width="21.453125" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="36">
+    <row r="1" spans="1:16" ht="36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14273,7 +14275,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>880</v>
       </c>
@@ -14323,7 +14325,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>880</v>
       </c>
@@ -14373,7 +14375,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>887</v>
       </c>
@@ -14423,7 +14425,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>887</v>
       </c>
@@ -14470,7 +14472,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>887</v>
       </c>
@@ -14517,7 +14519,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>887</v>
       </c>
@@ -14564,7 +14566,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>887</v>
       </c>
@@ -14608,7 +14610,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>898</v>
       </c>
@@ -14655,7 +14657,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>898</v>
       </c>
@@ -14702,7 +14704,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>899</v>
       </c>
@@ -14752,7 +14754,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>902</v>
       </c>
@@ -14796,7 +14798,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>902</v>
       </c>
@@ -14846,7 +14848,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>902</v>
       </c>
@@ -14893,7 +14895,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>902</v>
       </c>
@@ -14943,7 +14945,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>902</v>
       </c>
@@ -14993,7 +14995,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>907</v>
       </c>
@@ -15040,7 +15042,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>907</v>
       </c>
@@ -15090,7 +15092,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>907</v>
       </c>
@@ -15137,7 +15139,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>912</v>
       </c>
@@ -15184,7 +15186,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>912</v>
       </c>
@@ -15231,7 +15233,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>912</v>
       </c>
@@ -15278,7 +15280,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>912</v>
       </c>
@@ -15325,7 +15327,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>912</v>
       </c>
@@ -15380,7 +15382,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15389,7 +15391,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15398,13 +15400,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:XFC36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="10.453125" customWidth="1"/>
     <col min="8" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16383">
+    <row r="1" spans="1:16383" x14ac:dyDescent="0.35">
       <c r="D1" s="85"/>
       <c r="E1" s="85"/>
       <c r="F1" s="85"/>
@@ -15423,7 +15425,7 @@
       <c r="O1" s="85"/>
       <c r="P1" s="85"/>
     </row>
-    <row r="2" spans="1:16383">
+    <row r="2" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>31</v>
       </c>
@@ -31839,7 +31841,7 @@
       <c r="XFB2" s="53"/>
       <c r="XFC2" s="53"/>
     </row>
-    <row r="3" spans="1:16383">
+    <row r="3" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A3" s="73">
         <v>22</v>
       </c>
@@ -31888,7 +31890,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:16383">
+    <row r="4" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A4" s="73">
         <v>23</v>
       </c>
@@ -31937,7 +31939,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:16383">
+    <row r="5" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A5" s="73">
         <v>24</v>
       </c>
@@ -31986,7 +31988,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:16383">
+    <row r="6" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A6" s="73">
         <v>25</v>
       </c>
@@ -32035,7 +32037,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:16383">
+    <row r="7" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A7" s="73">
         <v>60</v>
       </c>
@@ -32084,7 +32086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:16383">
+    <row r="8" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A8" s="73">
         <v>61</v>
       </c>
@@ -32133,7 +32135,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:16383">
+    <row r="9" spans="1:16383" x14ac:dyDescent="0.35">
       <c r="A9" s="73">
         <v>62</v>
       </c>
@@ -32182,7 +32184,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:16383">
+    <row r="10" spans="1:16383" x14ac:dyDescent="0.35">
       <c r="A10" s="73">
         <v>63</v>
       </c>
@@ -32231,7 +32233,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:16383">
+    <row r="11" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A11" s="73">
         <v>64</v>
       </c>
@@ -32280,7 +32282,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:16383">
+    <row r="12" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A12" s="73"/>
       <c r="B12" s="74"/>
       <c r="C12" s="75"/>
@@ -32298,7 +32300,7 @@
       <c r="O12" s="83"/>
       <c r="P12" s="82"/>
     </row>
-    <row r="13" spans="1:16383">
+    <row r="13" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A13" s="73">
         <v>65</v>
       </c>
@@ -32347,7 +32349,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:16383">
+    <row r="14" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A14" s="73">
         <v>66</v>
       </c>
@@ -32396,7 +32398,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:16383">
+    <row r="15" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A15" s="73">
         <v>67</v>
       </c>
@@ -32445,7 +32447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:16383">
+    <row r="16" spans="1:16383" x14ac:dyDescent="0.3">
       <c r="A16" s="73">
         <v>68</v>
       </c>
@@ -32494,7 +32496,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="73">
         <v>69</v>
       </c>
@@ -32543,7 +32545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="73">
         <v>97</v>
       </c>
@@ -32592,7 +32594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="73">
         <v>98</v>
       </c>
@@ -32641,7 +32643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="73">
         <v>99</v>
       </c>
@@ -32690,7 +32692,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="73">
         <v>100</v>
       </c>
@@ -32739,7 +32741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="73">
         <v>101</v>
       </c>
@@ -32788,7 +32790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="73">
         <v>102</v>
       </c>
@@ -32837,7 +32839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="73"/>
       <c r="B24" s="79"/>
       <c r="C24" s="19"/>
@@ -32855,7 +32857,7 @@
       <c r="O24" s="83"/>
       <c r="P24" s="82"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="73">
         <v>103</v>
       </c>
@@ -32904,7 +32906,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="73">
         <v>128</v>
       </c>
@@ -32953,7 +32955,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="73">
         <v>129</v>
       </c>
@@ -33002,7 +33004,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="73">
         <v>130</v>
       </c>
@@ -33051,7 +33053,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="73">
         <v>131</v>
       </c>
@@ -33100,7 +33102,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D30" s="86"/>
       <c r="E30" s="86"/>
       <c r="F30" s="86"/>
@@ -33139,7 +33141,7 @@
       </c>
       <c r="P30" s="86"/>
     </row>
-    <row r="36" spans="13:13">
+    <row r="36" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M36">
         <v>2</v>
       </c>
@@ -33158,7 +33160,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" style="57" customWidth="1"/>
     <col min="2" max="2" width="9.54296875" style="57" customWidth="1"/>
@@ -33171,7 +33173,7 @@
     <col min="13" max="16384" width="9.1796875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="70" customFormat="1">
+    <row r="1" spans="1:14" s="70" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B1" s="70" t="s">
         <v>398</v>
       </c>
@@ -33200,7 +33202,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="67">
         <v>2</v>
       </c>
@@ -33245,7 +33247,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="67">
         <v>6</v>
       </c>
@@ -33290,7 +33292,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="67">
         <v>7</v>
       </c>
@@ -33335,7 +33337,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="67">
         <v>8</v>
       </c>
@@ -33380,7 +33382,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="67">
         <v>9</v>
       </c>
@@ -33425,7 +33427,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="67">
         <v>10</v>
       </c>
@@ -33470,7 +33472,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="67">
         <v>16</v>
       </c>
@@ -33515,7 +33517,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="67">
         <v>20</v>
       </c>
@@ -33560,7 +33562,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="67">
         <v>21</v>
       </c>
@@ -33605,7 +33607,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="67">
         <v>22</v>
       </c>
@@ -33650,7 +33652,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="67">
         <v>23</v>
       </c>
@@ -33695,7 +33697,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="67">
         <v>24</v>
       </c>
@@ -33740,7 +33742,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="67">
         <v>28</v>
       </c>
@@ -33785,7 +33787,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="67"/>
       <c r="B15" s="65"/>
       <c r="C15" s="54"/>
@@ -33801,7 +33803,7 @@
       <c r="M15" s="69"/>
       <c r="N15" s="58"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="67">
         <v>1</v>
       </c>
@@ -33846,7 +33848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="67">
         <v>3</v>
       </c>
@@ -33891,7 +33893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="67">
         <v>4</v>
       </c>
@@ -33936,7 +33938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="67">
         <v>5</v>
       </c>
@@ -33981,7 +33983,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="67">
         <v>11</v>
       </c>
@@ -34026,7 +34028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="67">
         <v>12</v>
       </c>
@@ -34071,7 +34073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="67">
         <v>13</v>
       </c>
@@ -34116,7 +34118,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="67">
         <v>18</v>
       </c>
@@ -34161,7 +34163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="67">
         <v>19</v>
       </c>
@@ -34206,7 +34208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="67">
         <v>25</v>
       </c>
@@ -34251,7 +34253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="67">
         <v>27</v>
       </c>
@@ -34296,7 +34298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="67"/>
       <c r="B27" s="65"/>
       <c r="C27" s="58"/>
@@ -34312,7 +34314,7 @@
       <c r="M27" s="69"/>
       <c r="N27" s="58"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="67">
         <v>14</v>
       </c>
@@ -34357,7 +34359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="67">
         <v>15</v>
       </c>
@@ -34402,7 +34404,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="67">
         <v>17</v>
       </c>
@@ -34447,7 +34449,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="22.5" customHeight="1">
+    <row r="31" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="67">
         <v>26</v>
       </c>
@@ -34492,7 +34494,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="K32" s="66">
         <f>SUM(K2:K31)</f>
         <v>80308</v>
@@ -34515,7 +34517,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" style="57" customWidth="1"/>
     <col min="2" max="2" width="14.7265625" style="57" customWidth="1"/>
@@ -34526,7 +34528,7 @@
     <col min="10" max="16384" width="9.1796875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="70" customFormat="1">
+    <row r="1" spans="1:13" s="70" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B1" s="70" t="s">
         <v>398</v>
       </c>
@@ -34549,7 +34551,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="67">
         <v>2</v>
       </c>
@@ -34588,7 +34590,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="67">
         <v>6</v>
       </c>
@@ -34627,7 +34629,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="67">
         <v>7</v>
       </c>
@@ -34666,7 +34668,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="67">
         <v>8</v>
       </c>
@@ -34705,7 +34707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="67">
         <v>9</v>
       </c>
@@ -34746,7 +34748,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="67">
         <v>10</v>
       </c>
@@ -34785,7 +34787,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="67">
         <v>16</v>
       </c>
@@ -34824,7 +34826,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="67">
         <v>20</v>
       </c>
@@ -34865,7 +34867,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="67">
         <v>21</v>
       </c>
@@ -34906,7 +34908,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="67">
         <v>22</v>
       </c>
@@ -34947,7 +34949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="67">
         <v>23</v>
       </c>
@@ -34988,7 +34990,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="67">
         <v>24</v>
       </c>
@@ -35029,7 +35031,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="67">
         <v>28</v>
       </c>
@@ -35068,7 +35070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="67"/>
       <c r="B15" s="65"/>
       <c r="C15" s="54"/>
@@ -35083,7 +35085,7 @@
       <c r="L15" s="54"/>
       <c r="M15" s="58"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="67">
         <v>1</v>
       </c>
@@ -35122,7 +35124,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="67">
         <v>3</v>
       </c>
@@ -35161,7 +35163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="67">
         <v>4</v>
       </c>
@@ -35200,7 +35202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="67">
         <v>5</v>
       </c>
@@ -35241,7 +35243,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="67">
         <v>11</v>
       </c>
@@ -35280,7 +35282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="67">
         <v>12</v>
       </c>
@@ -35319,7 +35321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="67">
         <v>13</v>
       </c>
@@ -35358,7 +35360,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="67">
         <v>18</v>
       </c>
@@ -35399,7 +35401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="67">
         <v>19</v>
       </c>
@@ -35438,7 +35440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="67">
         <v>25</v>
       </c>
@@ -35479,7 +35481,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="67">
         <v>27</v>
       </c>
@@ -35518,7 +35520,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="67"/>
       <c r="B27" s="65"/>
       <c r="C27" s="58"/>
@@ -35533,7 +35535,7 @@
       <c r="L27" s="58"/>
       <c r="M27" s="58"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="67">
         <v>14</v>
       </c>
@@ -35574,7 +35576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="67">
         <v>15</v>
       </c>
@@ -35615,7 +35617,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="67">
         <v>17</v>
       </c>
@@ -35654,7 +35656,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="22.5" customHeight="1">
+    <row r="31" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="67">
         <v>26</v>
       </c>
@@ -35695,7 +35697,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="K32" s="66">
         <f>SUM(K2:K31)</f>
         <v>80308</v>
@@ -35711,7 +35713,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O136"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" style="33" customWidth="1"/>
     <col min="2" max="2" width="10.1796875" style="33" customWidth="1"/>
@@ -35729,7 +35731,7 @@
     <col min="14" max="16384" width="9.1796875" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="31" customFormat="1" ht="44.25" customHeight="1">
+    <row r="1" spans="1:15" s="31" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="32" t="s">
         <v>183</v>
       </c>
@@ -35773,7 +35775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33">
         <v>1</v>
       </c>
@@ -35823,7 +35825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33">
         <v>2</v>
       </c>
@@ -35874,7 +35876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33">
         <v>3</v>
       </c>
@@ -35925,7 +35927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>4</v>
       </c>
@@ -35976,7 +35978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="33">
         <v>5</v>
       </c>
@@ -36027,7 +36029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>6</v>
       </c>
@@ -36078,7 +36080,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="33">
         <v>7</v>
       </c>
@@ -36129,7 +36131,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>8</v>
       </c>
@@ -36180,7 +36182,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="33">
         <v>9</v>
       </c>
@@ -36231,7 +36233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>10</v>
       </c>
@@ -36282,7 +36284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="33">
         <v>11</v>
       </c>
@@ -36333,7 +36335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>12</v>
       </c>
@@ -36384,7 +36386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33">
         <v>13</v>
       </c>
@@ -36435,7 +36437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>14</v>
       </c>
@@ -36486,7 +36488,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="33">
         <v>15</v>
       </c>
@@ -36537,7 +36539,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>16</v>
       </c>
@@ -36588,7 +36590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="33">
         <v>17</v>
       </c>
@@ -36639,7 +36641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="41" customFormat="1">
+    <row r="19" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>18</v>
       </c>
@@ -36690,7 +36692,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="41" customFormat="1">
+    <row r="20" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>19</v>
       </c>
@@ -36741,7 +36743,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="41" customFormat="1">
+    <row r="21" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>20</v>
       </c>
@@ -36792,7 +36794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="41" customFormat="1">
+    <row r="22" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41">
         <v>21</v>
       </c>
@@ -36843,7 +36845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="41" customFormat="1">
+    <row r="23" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>22</v>
       </c>
@@ -36894,7 +36896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="41" customFormat="1">
+    <row r="24" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>23</v>
       </c>
@@ -36945,7 +36947,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="41" customFormat="1">
+    <row r="25" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>24</v>
       </c>
@@ -36996,7 +36998,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="41" customFormat="1">
+    <row r="26" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>25</v>
       </c>
@@ -37047,7 +37049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>26</v>
       </c>
@@ -37098,7 +37100,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
         <v>27</v>
       </c>
@@ -37149,7 +37151,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>28</v>
       </c>
@@ -37200,7 +37202,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
         <v>29</v>
       </c>
@@ -37251,7 +37253,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>30</v>
       </c>
@@ -37302,7 +37304,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>31</v>
       </c>
@@ -37353,7 +37355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>32</v>
       </c>
@@ -37404,7 +37406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
         <v>33</v>
       </c>
@@ -37455,7 +37457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>34</v>
       </c>
@@ -37506,7 +37508,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
         <v>35</v>
       </c>
@@ -37557,7 +37559,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>36</v>
       </c>
@@ -37608,7 +37610,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
         <v>37</v>
       </c>
@@ -37659,7 +37661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
         <v>38</v>
       </c>
@@ -37710,7 +37712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
         <v>39</v>
       </c>
@@ -37761,7 +37763,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>40</v>
       </c>
@@ -37812,7 +37814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
         <v>41</v>
       </c>
@@ -37863,7 +37865,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
         <v>42</v>
       </c>
@@ -37914,7 +37916,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>43</v>
       </c>
@@ -37965,7 +37967,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
         <v>44</v>
       </c>
@@ -38016,7 +38018,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
         <v>45</v>
       </c>
@@ -38067,7 +38069,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>46</v>
       </c>
@@ -38118,7 +38120,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
         <v>47</v>
       </c>
@@ -38169,7 +38171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>48</v>
       </c>
@@ -38220,7 +38222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
         <v>49</v>
       </c>
@@ -38271,7 +38273,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33">
         <v>50</v>
       </c>
@@ -38322,7 +38324,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="41" customFormat="1">
+    <row r="52" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="41">
         <v>51</v>
       </c>
@@ -38373,7 +38375,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="41" customFormat="1">
+    <row r="53" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="41">
         <v>52</v>
       </c>
@@ -38424,7 +38426,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="41" customFormat="1">
+    <row r="54" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="41">
         <v>53</v>
       </c>
@@ -38475,7 +38477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="41" customFormat="1">
+    <row r="55" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="41">
         <v>54</v>
       </c>
@@ -38526,7 +38528,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:15" s="41" customFormat="1">
+    <row r="56" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="41">
         <v>55</v>
       </c>
@@ -38577,7 +38579,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:15" s="41" customFormat="1">
+    <row r="57" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="41">
         <v>56</v>
       </c>
@@ -38628,7 +38630,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="41" customFormat="1">
+    <row r="58" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="41">
         <v>57</v>
       </c>
@@ -38679,7 +38681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:15" s="41" customFormat="1">
+    <row r="59" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="41">
         <v>58</v>
       </c>
@@ -38730,7 +38732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:15" s="41" customFormat="1">
+    <row r="60" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41">
         <v>59</v>
       </c>
@@ -38781,7 +38783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:15" s="41" customFormat="1">
+    <row r="61" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="41">
         <v>60</v>
       </c>
@@ -38832,7 +38834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:15" s="41" customFormat="1">
+    <row r="62" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="41">
         <v>61</v>
       </c>
@@ -38883,7 +38885,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:15" s="41" customFormat="1">
+    <row r="63" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="41">
         <v>62</v>
       </c>
@@ -38934,7 +38936,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:15" s="41" customFormat="1">
+    <row r="64" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="41">
         <v>63</v>
       </c>
@@ -38985,7 +38987,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="1:15" s="41" customFormat="1">
+    <row r="65" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="41">
         <v>64</v>
       </c>
@@ -39036,7 +39038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:15" s="41" customFormat="1">
+    <row r="66" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="41">
         <v>65</v>
       </c>
@@ -39087,7 +39089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:15" s="41" customFormat="1">
+    <row r="67" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="41">
         <v>66</v>
       </c>
@@ -39137,7 +39139,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="41" customFormat="1">
+    <row r="68" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="41">
         <v>67</v>
       </c>
@@ -39188,7 +39190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="41" customFormat="1">
+    <row r="69" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="41">
         <v>68</v>
       </c>
@@ -39239,7 +39241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:15" s="41" customFormat="1">
+    <row r="70" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41">
         <v>69</v>
       </c>
@@ -39290,7 +39292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="33">
         <v>70</v>
       </c>
@@ -39341,7 +39343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="33">
         <v>71</v>
       </c>
@@ -39392,7 +39394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="33">
         <v>72</v>
       </c>
@@ -39443,7 +39445,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="33">
         <v>73</v>
       </c>
@@ -39494,7 +39496,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="33">
         <v>74</v>
       </c>
@@ -39545,7 +39547,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="33">
         <v>75</v>
       </c>
@@ -39596,7 +39598,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="33">
         <v>76</v>
       </c>
@@ -39647,7 +39649,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="33">
         <v>77</v>
       </c>
@@ -39698,7 +39700,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="33">
         <v>78</v>
       </c>
@@ -39749,7 +39751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="33">
         <v>79</v>
       </c>
@@ -39800,7 +39802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="33">
         <v>80</v>
       </c>
@@ -39851,7 +39853,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="33">
         <v>81</v>
       </c>
@@ -39902,7 +39904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="33">
         <v>82</v>
       </c>
@@ -39953,7 +39955,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="33">
         <v>83</v>
       </c>
@@ -40004,7 +40006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="33">
         <v>84</v>
       </c>
@@ -40055,7 +40057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="33">
         <v>85</v>
       </c>
@@ -40106,7 +40108,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="33">
         <v>86</v>
       </c>
@@ -40157,7 +40159,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="33">
         <v>87</v>
       </c>
@@ -40208,7 +40210,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="89" spans="1:15" s="41" customFormat="1">
+    <row r="89" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="41">
         <v>88</v>
       </c>
@@ -40259,7 +40261,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="1:15" s="41" customFormat="1">
+    <row r="90" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="41">
         <v>89</v>
       </c>
@@ -40310,7 +40312,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:15" s="41" customFormat="1">
+    <row r="91" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="41">
         <v>90</v>
       </c>
@@ -40361,7 +40363,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:15" s="41" customFormat="1">
+    <row r="92" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41">
         <v>91</v>
       </c>
@@ -40412,7 +40414,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:15" s="41" customFormat="1">
+    <row r="93" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="41">
         <v>92</v>
       </c>
@@ -40462,7 +40464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="41" customFormat="1">
+    <row r="94" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="41">
         <v>93</v>
       </c>
@@ -40512,7 +40514,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:15" s="41" customFormat="1">
+    <row r="95" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="41">
         <v>94</v>
       </c>
@@ -40563,7 +40565,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="41" customFormat="1">
+    <row r="96" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="41">
         <v>95</v>
       </c>
@@ -40613,7 +40615,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:15" s="41" customFormat="1">
+    <row r="97" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="41">
         <v>96</v>
       </c>
@@ -40664,7 +40666,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:15" s="41" customFormat="1">
+    <row r="98" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="41">
         <v>97</v>
       </c>
@@ -40714,7 +40716,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:15" s="41" customFormat="1">
+    <row r="99" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="41">
         <v>98</v>
       </c>
@@ -40764,7 +40766,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:15" s="41" customFormat="1">
+    <row r="100" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="41">
         <v>99</v>
       </c>
@@ -40814,7 +40816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:15" s="41" customFormat="1">
+    <row r="101" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="41">
         <v>100</v>
       </c>
@@ -40864,7 +40866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:15" s="41" customFormat="1" ht="13.5" customHeight="1">
+    <row r="102" spans="1:15" s="41" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41">
         <v>101</v>
       </c>
@@ -40914,7 +40916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="1:15" s="41" customFormat="1" ht="17.25" customHeight="1">
+    <row r="103" spans="1:15" s="41" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="41">
         <v>102</v>
       </c>
@@ -40964,7 +40966,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:15" s="41" customFormat="1" ht="14.5">
+    <row r="104" spans="1:15" s="41" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="41">
         <v>103</v>
       </c>
@@ -41014,7 +41016,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="33">
         <v>104</v>
       </c>
@@ -41064,7 +41066,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="33">
         <v>105</v>
       </c>
@@ -41114,7 +41116,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="33">
         <v>106</v>
       </c>
@@ -41164,7 +41166,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="33">
         <v>107</v>
       </c>
@@ -41214,7 +41216,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="33">
         <v>108</v>
       </c>
@@ -41264,7 +41266,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33">
         <v>109</v>
       </c>
@@ -41314,7 +41316,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="33">
         <v>110</v>
       </c>
@@ -41364,7 +41366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="33">
         <v>111</v>
       </c>
@@ -41414,7 +41416,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="33">
         <v>112</v>
       </c>
@@ -41464,7 +41466,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="33">
         <v>113</v>
       </c>
@@ -41514,7 +41516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="33">
         <v>114</v>
       </c>
@@ -41561,7 +41563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="33">
         <v>115</v>
       </c>
@@ -41611,7 +41613,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="33">
         <v>116</v>
       </c>
@@ -41661,7 +41663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="33">
         <v>117</v>
       </c>
@@ -41710,7 +41712,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="119" spans="1:15" s="41" customFormat="1">
+    <row r="119" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="41">
         <v>118</v>
       </c>
@@ -41759,7 +41761,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:15" s="41" customFormat="1">
+    <row r="120" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="41">
         <v>119</v>
       </c>
@@ -41808,7 +41810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:15" s="41" customFormat="1">
+    <row r="121" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" s="41">
         <v>120</v>
       </c>
@@ -41857,7 +41859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:15" s="41" customFormat="1">
+    <row r="122" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" s="41">
         <v>121</v>
       </c>
@@ -41906,7 +41908,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:15" s="41" customFormat="1">
+    <row r="123" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="41">
         <v>122</v>
       </c>
@@ -41955,7 +41957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:15" s="41" customFormat="1">
+    <row r="124" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="41">
         <v>123</v>
       </c>
@@ -42005,7 +42007,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="33">
         <v>124</v>
       </c>
@@ -42054,7 +42056,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="33">
         <v>125</v>
       </c>
@@ -42103,7 +42105,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="33">
         <v>126</v>
       </c>
@@ -42152,7 +42154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="33">
         <v>127</v>
       </c>
@@ -42201,7 +42203,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="129" spans="1:15" s="41" customFormat="1">
+    <row r="129" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="41">
         <v>128</v>
       </c>
@@ -42250,7 +42252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:15" s="41" customFormat="1">
+    <row r="130" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="41">
         <v>129</v>
       </c>
@@ -42299,7 +42301,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:15" s="41" customFormat="1">
+    <row r="131" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" s="41">
         <v>130</v>
       </c>
@@ -42348,7 +42350,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="132" spans="1:15" s="41" customFormat="1">
+    <row r="132" spans="1:15" s="41" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="41">
         <v>131</v>
       </c>
@@ -42397,7 +42399,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:15">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E136" s="37"/>
       <c r="F136" s="29" t="s">
         <v>265</v>
@@ -42445,7 +42447,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AC175"/>
-  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="88"/>
     <col min="2" max="3" width="15" style="88" customWidth="1"/>
@@ -42461,7 +42463,7 @@
     <col min="14" max="16384" width="12.1796875" style="88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="36">
+    <row r="1" spans="1:14" ht="36" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>183</v>
       </c>
@@ -42505,7 +42507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="89">
         <v>46028</v>
       </c>
@@ -42552,7 +42554,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="90" t="s">
         <v>333</v>
       </c>
@@ -42600,7 +42602,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="90" t="s">
         <v>334</v>
       </c>
@@ -42648,7 +42650,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="89">
         <v>46028</v>
       </c>
@@ -42695,7 +42697,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="89">
         <v>46028</v>
       </c>
@@ -42742,7 +42744,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="89">
         <v>46059</v>
       </c>
@@ -42788,7 +42790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="89">
         <v>46059</v>
       </c>
@@ -42834,7 +42836,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="89">
         <v>46059</v>
       </c>
@@ -42881,7 +42883,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="89">
         <v>46059</v>
       </c>
@@ -42928,7 +42930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="89">
         <v>46059</v>
       </c>
@@ -42974,7 +42976,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="89">
         <v>46059</v>
       </c>
@@ -43020,7 +43022,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="92">
         <v>46059</v>
       </c>
@@ -43066,7 +43068,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="89">
         <v>46087</v>
       </c>
@@ -43110,7 +43112,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="89">
         <v>46087</v>
       </c>
@@ -43154,7 +43156,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="89">
         <v>46087</v>
       </c>
@@ -43198,7 +43200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="89">
         <v>46087</v>
       </c>
@@ -43242,7 +43244,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="89">
         <v>46087</v>
       </c>
@@ -43286,7 +43288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="89">
         <v>46087</v>
       </c>
@@ -43330,7 +43332,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="89">
         <v>46087</v>
       </c>
@@ -43374,7 +43376,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="89">
         <v>46118</v>
       </c>
@@ -43418,7 +43420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="89">
         <v>46118</v>
       </c>
@@ -43462,7 +43464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="89">
         <v>46118</v>
       </c>
@@ -43506,7 +43508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="89">
         <v>46118</v>
       </c>
@@ -43550,7 +43552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="89">
         <v>46118</v>
       </c>
@@ -43595,7 +43597,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="89">
         <v>46118</v>
       </c>
@@ -43640,7 +43642,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="89">
         <v>46118</v>
       </c>
@@ -43684,7 +43686,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="89">
         <v>46118</v>
       </c>
@@ -43728,7 +43730,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="89">
         <v>46118</v>
       </c>
@@ -43774,7 +43776,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="89">
         <v>46118</v>
       </c>
@@ -43820,7 +43822,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="89">
         <v>46148</v>
       </c>
@@ -43866,7 +43868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="89">
         <v>46148</v>
       </c>
@@ -43912,7 +43914,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="89">
         <v>46148</v>
       </c>
@@ -43958,7 +43960,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="89">
         <v>46148</v>
       </c>
@@ -44004,7 +44006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="89">
         <v>46148</v>
       </c>
@@ -44050,7 +44052,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="89">
         <v>46148</v>
       </c>
@@ -44096,7 +44098,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="96">
         <v>46148</v>
       </c>
@@ -44142,7 +44144,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="89">
         <v>46148</v>
       </c>
@@ -44188,7 +44190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="89">
         <v>46240</v>
       </c>
@@ -44234,7 +44236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="89">
         <v>46240</v>
       </c>
@@ -44280,7 +44282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="89">
         <v>46240</v>
       </c>
@@ -44326,7 +44328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="89">
         <v>46240</v>
       </c>
@@ -44372,7 +44374,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="89">
         <v>46240</v>
       </c>
@@ -44418,7 +44420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="89">
         <v>46271</v>
       </c>
@@ -44464,7 +44466,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="89">
         <v>46271</v>
       </c>
@@ -44510,7 +44512,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="89">
         <v>46271</v>
       </c>
@@ -44556,7 +44558,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="89">
         <v>46271</v>
       </c>
@@ -44602,7 +44604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="89">
         <v>46271</v>
       </c>
@@ -44648,7 +44650,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:29">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A49" s="89">
         <v>46271</v>
       </c>
@@ -44694,7 +44696,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:29">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A50" s="89">
         <v>46271</v>
       </c>
@@ -44740,7 +44742,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:29">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A51" s="89">
         <v>46271</v>
       </c>
@@ -44786,7 +44788,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:29">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A52" s="89">
         <v>46271</v>
       </c>
@@ -44832,7 +44834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:29">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A53" s="89">
         <v>46271</v>
       </c>
@@ -44878,7 +44880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:29">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A54" s="89">
         <v>46271</v>
       </c>
@@ -44924,7 +44926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:29">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A55" s="89">
         <v>46271</v>
       </c>
@@ -44970,7 +44972,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:29">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A56" s="89">
         <v>46301</v>
       </c>
@@ -45016,7 +45018,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:29">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A57" s="89">
         <v>46301</v>
       </c>
@@ -45062,7 +45064,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:29">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A58" s="89">
         <v>46301</v>
       </c>
@@ -45106,7 +45108,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:29">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A59" s="89">
         <v>46301</v>
       </c>
@@ -45152,7 +45154,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:29">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A60" s="89">
         <v>46301</v>
       </c>
@@ -45198,7 +45200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:29">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A61" s="89">
         <v>46332</v>
       </c>
@@ -45244,7 +45246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:29">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A62" s="89">
         <v>46332</v>
       </c>
@@ -45290,7 +45292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:29">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A63" s="89">
         <v>46332</v>
       </c>
@@ -45336,7 +45338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:29">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64" s="89">
         <v>46332</v>
       </c>
@@ -45385,7 +45387,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="89">
         <v>46332</v>
       </c>
@@ -45429,7 +45431,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="89">
         <v>46332</v>
       </c>
@@ -45475,7 +45477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="89">
         <v>46332</v>
       </c>
@@ -45521,7 +45523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="89">
         <v>46332</v>
       </c>
@@ -45567,7 +45569,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="89">
         <v>46362</v>
       </c>
@@ -45613,7 +45615,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="89">
         <v>46362</v>
       </c>
@@ -45659,7 +45661,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="89">
         <v>46362</v>
       </c>
@@ -45705,7 +45707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="89">
         <v>46362</v>
       </c>
@@ -45751,7 +45753,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="89">
         <v>46362</v>
       </c>
@@ -45797,7 +45799,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="89">
         <v>46362</v>
       </c>
@@ -45843,7 +45845,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="89">
         <v>46362</v>
       </c>
@@ -45889,7 +45891,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="89">
         <v>46362</v>
       </c>
@@ -45935,7 +45937,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="89">
         <v>46362</v>
       </c>
@@ -45981,7 +45983,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="89">
         <v>46362</v>
       </c>
@@ -46027,7 +46029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="89">
         <v>46362</v>
       </c>
@@ -46073,7 +46075,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="89">
         <v>46362</v>
       </c>
@@ -46119,7 +46121,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="89">
         <v>46362</v>
       </c>
@@ -46165,7 +46167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="33" t="s">
         <v>585</v>
       </c>
@@ -46211,7 +46213,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="33" t="s">
         <v>585</v>
       </c>
@@ -46257,7 +46259,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="33" t="s">
         <v>585</v>
       </c>
@@ -46303,7 +46305,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="33" t="s">
         <v>585</v>
       </c>
@@ -46349,7 +46351,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="33" t="s">
         <v>585</v>
       </c>
@@ -46395,7 +46397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="33" t="s">
         <v>585</v>
       </c>
@@ -46441,7 +46443,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="33" t="s">
         <v>585</v>
       </c>
@@ -46487,7 +46489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="33" t="s">
         <v>585</v>
       </c>
@@ -46533,7 +46535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="33" t="s">
         <v>585</v>
       </c>
@@ -46579,7 +46581,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="33" t="s">
         <v>585</v>
       </c>
@@ -46625,7 +46627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="33" t="s">
         <v>585</v>
       </c>
@@ -46671,7 +46673,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="33" t="s">
         <v>585</v>
       </c>
@@ -46717,7 +46719,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="33" t="s">
         <v>585</v>
       </c>
@@ -46763,7 +46765,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="33" t="s">
         <v>585</v>
       </c>
@@ -46809,7 +46811,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="33" t="s">
         <v>585</v>
       </c>
@@ -46855,7 +46857,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="33" t="s">
         <v>585</v>
       </c>
@@ -46901,7 +46903,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="33" t="s">
         <v>586</v>
       </c>
@@ -46947,7 +46949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="33" t="s">
         <v>586</v>
       </c>
@@ -46993,7 +46995,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="33" t="s">
         <v>586</v>
       </c>
@@ -47039,7 +47041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="33" t="s">
         <v>586</v>
       </c>
@@ -47085,7 +47087,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="89" t="s">
         <v>586</v>
       </c>
@@ -47131,7 +47133,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="33" t="s">
         <v>586</v>
       </c>
@@ -47177,7 +47179,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="33" t="s">
         <v>586</v>
       </c>
@@ -47223,7 +47225,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="33" t="s">
         <v>589</v>
       </c>
@@ -47269,7 +47271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="33" t="s">
         <v>589</v>
       </c>
@@ -47315,7 +47317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="33" t="s">
         <v>589</v>
       </c>
@@ -47361,7 +47363,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="33" t="s">
         <v>589</v>
       </c>
@@ -47407,7 +47409,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="33" t="s">
         <v>589</v>
       </c>
@@ -47453,7 +47455,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="33" t="s">
         <v>589</v>
       </c>
@@ -47499,7 +47501,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="33" t="s">
         <v>589</v>
       </c>
@@ -47545,7 +47547,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="33" t="s">
         <v>589</v>
       </c>
@@ -47591,7 +47593,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="33" t="s">
         <v>589</v>
       </c>
@@ -47637,7 +47639,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="33" t="s">
         <v>605</v>
       </c>
@@ -47683,7 +47685,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="33" t="s">
         <v>605</v>
       </c>
@@ -47729,7 +47731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="33" t="s">
         <v>605</v>
       </c>
@@ -47775,7 +47777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="33" t="s">
         <v>605</v>
       </c>
@@ -47821,7 +47823,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="33" t="s">
         <v>605</v>
       </c>
@@ -47867,7 +47869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="33" t="s">
         <v>605</v>
       </c>
@@ -47913,7 +47915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="33" t="s">
         <v>605</v>
       </c>
@@ -47959,7 +47961,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="33" t="s">
         <v>619</v>
       </c>
@@ -48005,7 +48007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="33" t="s">
         <v>619</v>
       </c>
@@ -48051,7 +48053,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="38" t="s">
         <v>619</v>
       </c>
@@ -48097,7 +48099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="33" t="s">
         <v>619</v>
       </c>
@@ -48143,7 +48145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="38" t="s">
         <v>619</v>
       </c>
@@ -48189,7 +48191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="38" t="s">
         <v>619</v>
       </c>
@@ -48235,7 +48237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="38" t="s">
         <v>619</v>
       </c>
@@ -48281,7 +48283,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="33" t="s">
         <v>619</v>
       </c>
@@ -48327,7 +48329,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="38" t="s">
         <v>619</v>
       </c>
@@ -48373,7 +48375,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="38" t="s">
         <v>628</v>
       </c>
@@ -48419,7 +48421,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="38" t="s">
         <v>628</v>
       </c>
@@ -48465,7 +48467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="38" t="s">
         <v>628</v>
       </c>
@@ -48511,7 +48513,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="38" t="s">
         <v>628</v>
       </c>
@@ -48557,7 +48559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="33" t="s">
         <v>628</v>
       </c>
@@ -48603,7 +48605,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>628</v>
       </c>
@@ -48649,7 +48651,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="38" t="s">
         <v>628</v>
       </c>
@@ -48695,7 +48697,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="38" t="s">
         <v>628</v>
       </c>
@@ -48741,7 +48743,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="33" t="s">
         <v>628</v>
       </c>
@@ -48787,7 +48789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="33" t="s">
         <v>631</v>
       </c>
@@ -48833,7 +48835,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="38" t="s">
         <v>631</v>
       </c>
@@ -48879,7 +48881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="38" t="s">
         <v>631</v>
       </c>
@@ -48925,7 +48927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="38" t="s">
         <v>631</v>
       </c>
@@ -48971,7 +48973,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="38" t="s">
         <v>631</v>
       </c>
@@ -49017,7 +49019,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="38" t="s">
         <v>631</v>
       </c>
@@ -49063,7 +49065,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="33" t="s">
         <v>631</v>
       </c>
@@ -49109,7 +49111,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="89" t="s">
         <v>634</v>
       </c>
@@ -49155,7 +49157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="38" t="s">
         <v>634</v>
       </c>
@@ -49201,7 +49203,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="33" t="s">
         <v>634</v>
       </c>
@@ -49247,7 +49249,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="38" t="s">
         <v>634</v>
       </c>
@@ -49293,7 +49295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="38" t="s">
         <v>634</v>
       </c>
@@ -49339,7 +49341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="89" t="s">
         <v>634</v>
       </c>
@@ -49385,7 +49387,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="33" t="s">
         <v>634</v>
       </c>
@@ -49431,7 +49433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="89" t="s">
         <v>640</v>
       </c>
@@ -49475,7 +49477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="38" t="s">
         <v>640</v>
       </c>
@@ -49519,7 +49521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="38" t="s">
         <v>640</v>
       </c>
@@ -49563,7 +49565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="33" t="s">
         <v>640</v>
       </c>
@@ -49607,7 +49609,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="33" t="s">
         <v>640</v>
       </c>
@@ -49651,7 +49653,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="38" t="s">
         <v>643</v>
       </c>
@@ -49695,7 +49697,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="38" t="s">
         <v>643</v>
       </c>
@@ -49739,7 +49741,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="38" t="s">
         <v>643</v>
       </c>
@@ -49783,7 +49785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="38" t="s">
         <v>643</v>
       </c>
@@ -49827,7 +49829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="33" t="s">
         <v>643</v>
       </c>
@@ -49871,7 +49873,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="33" t="s">
         <v>646</v>
       </c>
@@ -49915,7 +49917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="89" t="s">
         <v>646</v>
       </c>
@@ -49961,7 +49963,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="38" t="s">
         <v>646</v>
       </c>
@@ -50005,7 +50007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="38" t="s">
         <v>646</v>
       </c>
@@ -50049,7 +50051,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="89" t="s">
         <v>646</v>
       </c>
@@ -50095,7 +50097,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="33" t="s">
         <v>646</v>
       </c>
@@ -50139,7 +50141,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="89" t="s">
         <v>651</v>
       </c>
@@ -50183,7 +50185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="89" t="s">
         <v>651</v>
       </c>
@@ -50227,7 +50229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="89" t="s">
         <v>651</v>
       </c>
@@ -50271,7 +50273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="33" t="s">
         <v>651</v>
       </c>
@@ -50315,7 +50317,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="89" t="s">
         <v>651</v>
       </c>
@@ -50359,7 +50361,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="J175" s="88">
         <f>SUM(J2:J174)</f>
         <v>2220858</v>
@@ -50386,7 +50388,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N152"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="17.81640625" customWidth="1"/>
@@ -50403,7 +50405,7 @@
     <col min="14" max="14" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="36">
+    <row r="1" spans="1:14" ht="36" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>183</v>
       </c>
@@ -50447,7 +50449,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="97">
         <v>46029</v>
       </c>
@@ -50491,7 +50493,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="97">
         <v>46029</v>
       </c>
@@ -50535,7 +50537,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="97">
         <v>46029</v>
       </c>
@@ -50579,7 +50581,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="97">
         <v>46060</v>
       </c>
@@ -50623,7 +50625,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="97">
         <v>46088</v>
       </c>
@@ -50667,7 +50669,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="97">
         <v>46088</v>
       </c>
@@ -50711,7 +50713,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="97">
         <v>46088</v>
       </c>
@@ -50755,7 +50757,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="97">
         <v>46088</v>
       </c>
@@ -50799,7 +50801,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="97">
         <v>46088</v>
       </c>
@@ -50843,7 +50845,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="97">
         <v>46180</v>
       </c>
@@ -50887,7 +50889,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="97">
         <v>46180</v>
       </c>
@@ -50931,7 +50933,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="97">
         <v>46180</v>
       </c>
@@ -50975,7 +50977,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="97">
         <v>46180</v>
       </c>
@@ -51019,7 +51021,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="97">
         <v>46180</v>
       </c>
@@ -51063,7 +51065,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="97">
         <v>46180</v>
       </c>
@@ -51107,7 +51109,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="97">
         <v>46180</v>
       </c>
@@ -51151,7 +51153,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="97">
         <v>46180</v>
       </c>
@@ -51195,7 +51197,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="97">
         <v>46180</v>
       </c>
@@ -51239,7 +51241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="97">
         <v>46180</v>
       </c>
@@ -51283,7 +51285,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="97">
         <v>46180</v>
       </c>
@@ -51327,7 +51329,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="97">
         <v>46180</v>
       </c>
@@ -51371,7 +51373,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="97">
         <v>46180</v>
       </c>
@@ -51415,7 +51417,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="97">
         <v>46180</v>
       </c>
@@ -51459,7 +51461,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="97">
         <v>46180</v>
       </c>
@@ -51503,7 +51505,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="97">
         <v>46180</v>
       </c>
@@ -51547,7 +51549,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="97">
         <v>46180</v>
       </c>
@@ -51591,7 +51593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="97">
         <v>46210</v>
       </c>
@@ -51635,7 +51637,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="97">
         <v>46210</v>
       </c>
@@ -51679,7 +51681,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="97">
         <v>46209</v>
       </c>
@@ -51723,7 +51725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="97">
         <v>46210</v>
       </c>
@@ -51767,7 +51769,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="97">
         <v>46210</v>
       </c>
@@ -51811,7 +51813,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="97">
         <v>46210</v>
       </c>
@@ -51855,7 +51857,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="97">
         <v>46209</v>
       </c>
@@ -51899,7 +51901,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="97">
         <v>46241</v>
       </c>
@@ -51943,7 +51945,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="97">
         <v>46241</v>
       </c>
@@ -51987,7 +51989,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="97">
         <v>46241</v>
       </c>
@@ -52031,7 +52033,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="97">
         <v>46241</v>
       </c>
@@ -52075,7 +52077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="97">
         <v>46241</v>
       </c>
@@ -52119,7 +52121,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="97">
         <v>46241</v>
       </c>
@@ -52163,7 +52165,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="97">
         <v>46241</v>
       </c>
@@ -52207,7 +52209,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="97">
         <v>46272</v>
       </c>
@@ -52251,7 +52253,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="97">
         <v>46272</v>
       </c>
@@ -52295,7 +52297,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="97">
         <v>46272</v>
       </c>
@@ -52339,7 +52341,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="97">
         <v>46272</v>
       </c>
@@ -52383,7 +52385,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="97">
         <v>46272</v>
       </c>
@@ -52427,7 +52429,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="97">
         <v>46272</v>
       </c>
@@ -52471,7 +52473,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="97">
         <v>46302</v>
       </c>
@@ -52515,7 +52517,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="97">
         <v>46301</v>
       </c>
@@ -52559,7 +52561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="97">
         <v>46302</v>
       </c>
@@ -52603,7 +52605,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>709</v>
       </c>
@@ -52647,7 +52649,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>709</v>
       </c>
@@ -52691,7 +52693,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>712</v>
       </c>
@@ -52735,7 +52737,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>709</v>
       </c>
@@ -52779,7 +52781,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>709</v>
       </c>
@@ -52823,7 +52825,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>709</v>
       </c>
@@ -52867,7 +52869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>709</v>
       </c>
@@ -52911,7 +52913,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>709</v>
       </c>
@@ -52955,7 +52957,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>709</v>
       </c>
@@ -52999,7 +53001,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>709</v>
       </c>
@@ -53043,7 +53045,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>709</v>
       </c>
@@ -53087,7 +53089,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>722</v>
       </c>
@@ -53131,7 +53133,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>722</v>
       </c>
@@ -53175,7 +53177,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>722</v>
       </c>
@@ -53219,7 +53221,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>722</v>
       </c>
@@ -53263,7 +53265,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>722</v>
       </c>
@@ -53307,7 +53309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>722</v>
       </c>
@@ -53351,7 +53353,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>725</v>
       </c>
@@ -53395,7 +53397,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>725</v>
       </c>
@@ -53439,7 +53441,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>725</v>
       </c>
@@ -53483,7 +53485,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>725</v>
       </c>
@@ -53527,7 +53529,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>725</v>
       </c>
@@ -53571,7 +53573,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>725</v>
       </c>
@@ -53615,7 +53617,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>733</v>
       </c>
@@ -53659,7 +53661,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>733</v>
       </c>
@@ -53703,7 +53705,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>733</v>
       </c>
@@ -53747,7 +53749,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>733</v>
       </c>
@@ -53791,7 +53793,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>733</v>
       </c>
@@ -53835,7 +53837,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>733</v>
       </c>
@@ -53879,7 +53881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>733</v>
       </c>
@@ -53923,7 +53925,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>741</v>
       </c>
@@ -53967,7 +53969,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>741</v>
       </c>
@@ -54011,7 +54013,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>741</v>
       </c>
@@ -54055,7 +54057,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>741</v>
       </c>
@@ -54099,7 +54101,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>747</v>
       </c>
@@ -54143,7 +54145,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>747</v>
       </c>
@@ -54187,7 +54189,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>747</v>
       </c>
@@ -54231,7 +54233,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>747</v>
       </c>
@@ -54275,7 +54277,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>750</v>
       </c>
@@ -54319,7 +54321,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>750</v>
       </c>
@@ -54363,7 +54365,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>750</v>
       </c>
@@ -54407,7 +54409,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>750</v>
       </c>
@@ -54451,7 +54453,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>750</v>
       </c>
@@ -54495,7 +54497,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>750</v>
       </c>
@@ -54539,7 +54541,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>750</v>
       </c>
@@ -54583,7 +54585,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>750</v>
       </c>
@@ -54627,7 +54629,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>750</v>
       </c>
@@ -54671,7 +54673,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>750</v>
       </c>
@@ -54715,7 +54717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>750</v>
       </c>
@@ -54759,7 +54761,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>750</v>
       </c>
@@ -54803,7 +54805,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>750</v>
       </c>
@@ -54847,7 +54849,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>756</v>
       </c>
@@ -54891,7 +54893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>756</v>
       </c>
@@ -54935,7 +54937,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>756</v>
       </c>
@@ -54979,7 +54981,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>756</v>
       </c>
@@ -55023,7 +55025,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>756</v>
       </c>
@@ -55067,7 +55069,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>756</v>
       </c>
@@ -55111,7 +55113,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>756</v>
       </c>
@@ -55155,7 +55157,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>756</v>
       </c>
@@ -55199,7 +55201,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>766</v>
       </c>
@@ -55243,7 +55245,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>766</v>
       </c>
@@ -55287,7 +55289,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>766</v>
       </c>
@@ -55331,7 +55333,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>766</v>
       </c>
@@ -55375,7 +55377,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>766</v>
       </c>
@@ -55419,7 +55421,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>768</v>
       </c>
@@ -55463,7 +55465,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>768</v>
       </c>
@@ -55507,7 +55509,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>768</v>
       </c>
@@ -55551,7 +55553,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>768</v>
       </c>
@@ -55595,7 +55597,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="97" t="s">
         <v>768</v>
       </c>
@@ -55639,7 +55641,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="97" t="s">
         <v>768</v>
       </c>
@@ -55683,7 +55685,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>768</v>
       </c>
@@ -55727,7 +55729,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>768</v>
       </c>
@@ -55771,7 +55773,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>768</v>
       </c>
@@ -55815,7 +55817,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>768</v>
       </c>
@@ -55859,7 +55861,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>768</v>
       </c>
@@ -55903,7 +55905,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>778</v>
       </c>
@@ -55947,7 +55949,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>778</v>
       </c>
@@ -55991,7 +55993,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>778</v>
       </c>
@@ -56035,7 +56037,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>778</v>
       </c>
@@ -56079,7 +56081,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>778</v>
       </c>
@@ -56123,7 +56125,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>778</v>
       </c>
@@ -56167,7 +56169,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>782</v>
       </c>
@@ -56211,7 +56213,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>782</v>
       </c>
@@ -56255,7 +56257,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>782</v>
       </c>
@@ -56299,7 +56301,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>782</v>
       </c>
@@ -56343,7 +56345,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>782</v>
       </c>
@@ -56387,7 +56389,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>782</v>
       </c>
@@ -56431,7 +56433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>782</v>
       </c>
@@ -56475,7 +56477,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>782</v>
       </c>
@@ -56519,7 +56521,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>782</v>
       </c>
@@ -56563,7 +56565,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>782</v>
       </c>
@@ -56607,7 +56609,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>797</v>
       </c>
@@ -56651,7 +56653,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>797</v>
       </c>
@@ -56695,7 +56697,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>797</v>
       </c>
@@ -56739,7 +56741,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>797</v>
       </c>
@@ -56783,7 +56785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>797</v>
       </c>
@@ -56827,7 +56829,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>797</v>
       </c>
@@ -56871,7 +56873,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>797</v>
       </c>
@@ -56915,7 +56917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>797</v>
       </c>
@@ -56959,7 +56961,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>801</v>
       </c>
@@ -57003,7 +57005,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>803</v>
       </c>
@@ -57047,7 +57049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="F152">
         <f>SUM(F2:F151)</f>
         <v>1531000</v>
@@ -57066,33 +57068,33 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="33"/>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="33"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="33"/>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="33"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="33"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="33"/>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="33"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="33"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="33"/>
     </row>
   </sheetData>
@@ -57103,7 +57105,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="9.1796875" hidden="1" customWidth="1"/>
